--- a/output/graficos_nacionales/plot_nacional_dispersion_e_supneta_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_dispersion_e_supneta_a_2024.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comunas'!$A$1:$D$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comunas'!$A$1:$D$330</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="346">
   <si>
     <t xml:space="preserve">Comuna</t>
   </si>
@@ -462,6 +462,9 @@
     <t xml:space="preserve">Río Ibáñez</t>
   </si>
   <si>
+    <t xml:space="preserve">Marchigüe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Petorca</t>
   </si>
   <si>
@@ -723,6 +726,9 @@
     <t xml:space="preserve">La Granja</t>
   </si>
   <si>
+    <t xml:space="preserve">Paihuano</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Antonio</t>
   </si>
   <si>
@@ -1017,7 +1023,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:44</t>
+    <t xml:space="preserve">2026-09-18 12:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -3453,13 +3459,13 @@
         <v>148</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>44.99</v>
+        <v>45.02</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>10063</v>
+        <v>10017</v>
       </c>
       <c r="D146" s="2" t="n">
-        <v>768021</v>
+        <v>736174</v>
       </c>
     </row>
     <row r="147">
@@ -3467,13 +3473,13 @@
         <v>149</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>44.98</v>
+        <v>44.99</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>5878</v>
+        <v>10063</v>
       </c>
       <c r="D147" s="2" t="n">
-        <v>634944</v>
+        <v>768021</v>
       </c>
     </row>
     <row r="148">
@@ -3484,10 +3490,10 @@
         <v>44.98</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>33655</v>
+        <v>5878</v>
       </c>
       <c r="D148" s="2" t="n">
-        <v>828127.5</v>
+        <v>634944</v>
       </c>
     </row>
     <row r="149">
@@ -3495,13 +3501,13 @@
         <v>151</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>44.85</v>
+        <v>44.98</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>83365</v>
+        <v>33655</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>793961</v>
+        <v>828127.5</v>
       </c>
     </row>
     <row r="150">
@@ -3509,13 +3515,13 @@
         <v>152</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>44.84</v>
+        <v>44.85</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>37737</v>
+        <v>83365</v>
       </c>
       <c r="D150" s="2" t="n">
-        <v>804688</v>
+        <v>793961</v>
       </c>
     </row>
     <row r="151">
@@ -3523,13 +3529,13 @@
         <v>153</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>44.79</v>
+        <v>44.84</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>17644</v>
+        <v>37737</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>797748</v>
+        <v>804688</v>
       </c>
     </row>
     <row r="152">
@@ -3537,13 +3543,13 @@
         <v>154</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>44.78</v>
+        <v>44.79</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>11090</v>
+        <v>17644</v>
       </c>
       <c r="D152" s="2" t="n">
-        <v>792662</v>
+        <v>797748</v>
       </c>
     </row>
     <row r="153">
@@ -3551,13 +3557,13 @@
         <v>155</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>44.7</v>
+        <v>44.78</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>14123</v>
+        <v>11090</v>
       </c>
       <c r="D153" s="2" t="n">
-        <v>652765</v>
+        <v>792662</v>
       </c>
     </row>
     <row r="154">
@@ -3565,13 +3571,13 @@
         <v>156</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>44.67</v>
+        <v>44.7</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>305686</v>
+        <v>14123</v>
       </c>
       <c r="D154" s="2" t="n">
-        <v>861891.5</v>
+        <v>652765</v>
       </c>
     </row>
     <row r="155">
@@ -3582,10 +3588,10 @@
         <v>44.67</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>4192</v>
+        <v>305686</v>
       </c>
       <c r="D155" s="2" t="n">
-        <v>836005</v>
+        <v>861891.5</v>
       </c>
     </row>
     <row r="156">
@@ -3593,13 +3599,13 @@
         <v>158</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>44.62</v>
+        <v>44.67</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>33498</v>
+        <v>4192</v>
       </c>
       <c r="D156" s="2" t="n">
-        <v>770961</v>
+        <v>836005</v>
       </c>
     </row>
     <row r="157">
@@ -3607,13 +3613,13 @@
         <v>159</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>44.57</v>
+        <v>44.62</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>21316</v>
+        <v>33498</v>
       </c>
       <c r="D157" s="2" t="n">
-        <v>748264</v>
+        <v>770961</v>
       </c>
     </row>
     <row r="158">
@@ -3621,13 +3627,13 @@
         <v>160</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>44.55</v>
+        <v>44.57</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>28231</v>
+        <v>21316</v>
       </c>
       <c r="D158" s="2" t="n">
-        <v>949249.5</v>
+        <v>748264</v>
       </c>
     </row>
     <row r="159">
@@ -3635,13 +3641,13 @@
         <v>161</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>44.5</v>
+        <v>44.55</v>
       </c>
       <c r="C159" s="2" t="n">
-        <v>14321</v>
+        <v>28231</v>
       </c>
       <c r="D159" s="2" t="n">
-        <v>931830</v>
+        <v>949249.5</v>
       </c>
     </row>
     <row r="160">
@@ -3649,13 +3655,13 @@
         <v>162</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>44.48</v>
+        <v>44.5</v>
       </c>
       <c r="C160" s="2" t="n">
-        <v>132290</v>
+        <v>14321</v>
       </c>
       <c r="D160" s="2" t="n">
-        <v>847730</v>
+        <v>931830</v>
       </c>
     </row>
     <row r="161">
@@ -3666,10 +3672,10 @@
         <v>44.48</v>
       </c>
       <c r="C161" s="2" t="n">
-        <v>10937</v>
+        <v>132290</v>
       </c>
       <c r="D161" s="2" t="n">
-        <v>765960</v>
+        <v>847730</v>
       </c>
     </row>
     <row r="162">
@@ -3677,13 +3683,13 @@
         <v>164</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>44.44</v>
+        <v>44.48</v>
       </c>
       <c r="C162" s="2" t="n">
-        <v>547</v>
+        <v>10937</v>
       </c>
       <c r="D162" s="2" t="n">
-        <v>920000</v>
+        <v>765960</v>
       </c>
     </row>
     <row r="163">
@@ -3691,13 +3697,13 @@
         <v>165</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>44.41</v>
+        <v>44.44</v>
       </c>
       <c r="C163" s="2" t="n">
-        <v>16180</v>
+        <v>547</v>
       </c>
       <c r="D163" s="2" t="n">
-        <v>736600</v>
+        <v>920000</v>
       </c>
     </row>
     <row r="164">
@@ -3705,13 +3711,13 @@
         <v>166</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>44.39</v>
+        <v>44.41</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>103953</v>
+        <v>16180</v>
       </c>
       <c r="D164" s="2" t="n">
-        <v>804938</v>
+        <v>736600</v>
       </c>
     </row>
     <row r="165">
@@ -3719,13 +3725,13 @@
         <v>167</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>44.33</v>
+        <v>44.39</v>
       </c>
       <c r="C165" s="2" t="n">
-        <v>25667</v>
+        <v>103953</v>
       </c>
       <c r="D165" s="2" t="n">
-        <v>720000</v>
+        <v>804938</v>
       </c>
     </row>
     <row r="166">
@@ -3733,13 +3739,13 @@
         <v>168</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>44.3</v>
+        <v>44.33</v>
       </c>
       <c r="C166" s="2" t="n">
-        <v>21981</v>
+        <v>25667</v>
       </c>
       <c r="D166" s="2" t="n">
-        <v>686945</v>
+        <v>720000</v>
       </c>
     </row>
     <row r="167">
@@ -3747,13 +3753,13 @@
         <v>169</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>44.22</v>
+        <v>44.3</v>
       </c>
       <c r="C167" s="2" t="n">
-        <v>37915</v>
+        <v>21981</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>717864</v>
+        <v>686945</v>
       </c>
     </row>
     <row r="168">
@@ -3761,13 +3767,13 @@
         <v>170</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>44.19</v>
+        <v>44.22</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>68300</v>
+        <v>37915</v>
       </c>
       <c r="D168" s="2" t="n">
-        <v>754760</v>
+        <v>717864</v>
       </c>
     </row>
     <row r="169">
@@ -3775,13 +3781,13 @@
         <v>171</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>44.18</v>
+        <v>44.19</v>
       </c>
       <c r="C169" s="2" t="n">
-        <v>8069</v>
+        <v>68300</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>684535</v>
+        <v>754760</v>
       </c>
     </row>
     <row r="170">
@@ -3789,13 +3795,13 @@
         <v>172</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>44.13</v>
+        <v>44.18</v>
       </c>
       <c r="C170" s="2" t="n">
-        <v>125772</v>
+        <v>8069</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>815318</v>
+        <v>684535</v>
       </c>
     </row>
     <row r="171">
@@ -3803,13 +3809,13 @@
         <v>173</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>44.06</v>
+        <v>44.13</v>
       </c>
       <c r="C171" s="2" t="n">
-        <v>15710</v>
+        <v>125772</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>834136.5</v>
+        <v>815318</v>
       </c>
     </row>
     <row r="172">
@@ -3817,13 +3823,13 @@
         <v>174</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>44.03</v>
+        <v>44.06</v>
       </c>
       <c r="C172" s="2" t="n">
-        <v>37082</v>
+        <v>15710</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>722010</v>
+        <v>834136.5</v>
       </c>
     </row>
     <row r="173">
@@ -3831,13 +3837,13 @@
         <v>175</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>44</v>
+        <v>44.03</v>
       </c>
       <c r="C173" s="2" t="n">
-        <v>38007</v>
+        <v>37082</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>857835</v>
+        <v>722010</v>
       </c>
     </row>
     <row r="174">
@@ -3845,13 +3851,13 @@
         <v>176</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>43.94</v>
+        <v>44</v>
       </c>
       <c r="C174" s="2" t="n">
-        <v>95139</v>
+        <v>38007</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>782283.5</v>
+        <v>857835</v>
       </c>
     </row>
     <row r="175">
@@ -3859,13 +3865,13 @@
         <v>177</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>43.89</v>
+        <v>43.94</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>31042</v>
+        <v>95139</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>956470</v>
+        <v>782283.5</v>
       </c>
     </row>
     <row r="176">
@@ -3873,13 +3879,13 @@
         <v>178</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>43.87</v>
+        <v>43.89</v>
       </c>
       <c r="C176" s="2" t="n">
-        <v>85854</v>
+        <v>31042</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>891703</v>
+        <v>956470</v>
       </c>
     </row>
     <row r="177">
@@ -3890,10 +3896,10 @@
         <v>43.87</v>
       </c>
       <c r="C177" s="2" t="n">
-        <v>21719</v>
+        <v>85854</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>727604</v>
+        <v>891703</v>
       </c>
     </row>
     <row r="178">
@@ -3901,13 +3907,13 @@
         <v>180</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>43.86</v>
+        <v>43.87</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>59571</v>
+        <v>21719</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>1046550</v>
+        <v>727604</v>
       </c>
     </row>
     <row r="179">
@@ -3915,13 +3921,13 @@
         <v>181</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>43.83</v>
+        <v>43.86</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>16941</v>
+        <v>59571</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>926878</v>
+        <v>1046550</v>
       </c>
     </row>
     <row r="180">
@@ -3929,13 +3935,13 @@
         <v>182</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>43.7</v>
+        <v>43.83</v>
       </c>
       <c r="C180" s="2" t="n">
-        <v>13688</v>
+        <v>16941</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>708251</v>
+        <v>926878</v>
       </c>
     </row>
     <row r="181">
@@ -3943,13 +3949,13 @@
         <v>183</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>43.65</v>
+        <v>43.7</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>14770</v>
+        <v>13688</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>1010010</v>
+        <v>708251</v>
       </c>
     </row>
     <row r="182">
@@ -3957,13 +3963,13 @@
         <v>184</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>43.64</v>
+        <v>43.65</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>20102</v>
+        <v>14770</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>750000</v>
+        <v>1010010</v>
       </c>
     </row>
     <row r="183">
@@ -3971,13 +3977,13 @@
         <v>185</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>43.58</v>
+        <v>43.64</v>
       </c>
       <c r="C183" s="2" t="n">
-        <v>16641</v>
+        <v>20102</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>824806.5</v>
+        <v>750000</v>
       </c>
     </row>
     <row r="184">
@@ -3985,13 +3991,13 @@
         <v>186</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>43.57</v>
+        <v>43.58</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>15595</v>
+        <v>16641</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>750964</v>
+        <v>824806.5</v>
       </c>
     </row>
     <row r="185">
@@ -3999,13 +4005,13 @@
         <v>187</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>43.55</v>
+        <v>43.57</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>84683</v>
+        <v>15595</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>706930</v>
+        <v>750964</v>
       </c>
     </row>
     <row r="186">
@@ -4016,10 +4022,10 @@
         <v>43.55</v>
       </c>
       <c r="C186" s="2" t="n">
-        <v>26787</v>
+        <v>84683</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>787500</v>
+        <v>706930</v>
       </c>
     </row>
     <row r="187">
@@ -4027,13 +4033,13 @@
         <v>189</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>43.52</v>
+        <v>43.55</v>
       </c>
       <c r="C187" s="2" t="n">
-        <v>5686</v>
+        <v>26787</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>657329</v>
+        <v>787500</v>
       </c>
     </row>
     <row r="188">
@@ -4041,13 +4047,13 @@
         <v>190</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>43.46</v>
+        <v>43.52</v>
       </c>
       <c r="C188" s="2" t="n">
-        <v>12548</v>
+        <v>5686</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>659530</v>
+        <v>657329</v>
       </c>
     </row>
     <row r="189">
@@ -4055,13 +4061,13 @@
         <v>191</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>43.43</v>
+        <v>43.46</v>
       </c>
       <c r="C189" s="2" t="n">
-        <v>32799</v>
+        <v>12548</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>676560</v>
+        <v>659530</v>
       </c>
     </row>
     <row r="190">
@@ -4072,10 +4078,10 @@
         <v>43.43</v>
       </c>
       <c r="C190" s="2" t="n">
-        <v>6305</v>
+        <v>32799</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>915140</v>
+        <v>676560</v>
       </c>
     </row>
     <row r="191">
@@ -4083,13 +4089,13 @@
         <v>193</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>43.42</v>
+        <v>43.43</v>
       </c>
       <c r="C191" s="2" t="n">
-        <v>9006</v>
+        <v>6305</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>872365</v>
+        <v>915140</v>
       </c>
     </row>
     <row r="192">
@@ -4097,13 +4103,13 @@
         <v>194</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>43.41</v>
+        <v>43.42</v>
       </c>
       <c r="C192" s="2" t="n">
-        <v>77539</v>
+        <v>9006</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>760300</v>
+        <v>872365</v>
       </c>
     </row>
     <row r="193">
@@ -4111,13 +4117,13 @@
         <v>195</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>43.39</v>
+        <v>43.41</v>
       </c>
       <c r="C193" s="2" t="n">
-        <v>127558</v>
+        <v>77539</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>1003691</v>
+        <v>760300</v>
       </c>
     </row>
     <row r="194">
@@ -4125,13 +4131,13 @@
         <v>196</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>43.38</v>
+        <v>43.39</v>
       </c>
       <c r="C194" s="2" t="n">
-        <v>168278</v>
+        <v>127558</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>802309</v>
+        <v>1003691</v>
       </c>
     </row>
     <row r="195">
@@ -4139,13 +4145,13 @@
         <v>197</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>43.28</v>
+        <v>43.38</v>
       </c>
       <c r="C195" s="2" t="n">
-        <v>54451</v>
+        <v>168278</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>892350</v>
+        <v>802309</v>
       </c>
     </row>
     <row r="196">
@@ -4153,13 +4159,13 @@
         <v>198</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>43.26</v>
+        <v>43.28</v>
       </c>
       <c r="C196" s="2" t="n">
-        <v>144642</v>
+        <v>54451</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>786347</v>
+        <v>892350</v>
       </c>
     </row>
     <row r="197">
@@ -4167,13 +4173,13 @@
         <v>199</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>43.24</v>
+        <v>43.26</v>
       </c>
       <c r="C197" s="2" t="n">
-        <v>51995</v>
+        <v>144642</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>700000</v>
+        <v>786347</v>
       </c>
     </row>
     <row r="198">
@@ -4181,13 +4187,13 @@
         <v>200</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>43.17</v>
+        <v>43.24</v>
       </c>
       <c r="C198" s="2" t="n">
-        <v>10742</v>
+        <v>51995</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>708568</v>
+        <v>700000</v>
       </c>
     </row>
     <row r="199">
@@ -4195,13 +4201,13 @@
         <v>201</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>43.15</v>
+        <v>43.17</v>
       </c>
       <c r="C199" s="2" t="n">
-        <v>27156</v>
+        <v>10742</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>691100</v>
+        <v>708568</v>
       </c>
     </row>
     <row r="200">
@@ -4209,13 +4215,13 @@
         <v>202</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>43.06</v>
+        <v>43.15</v>
       </c>
       <c r="C200" s="2" t="n">
-        <v>1522</v>
+        <v>27156</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>840454</v>
+        <v>691100</v>
       </c>
     </row>
     <row r="201">
@@ -4223,13 +4229,13 @@
         <v>203</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>42.97</v>
+        <v>43.06</v>
       </c>
       <c r="C201" s="2" t="n">
-        <v>14083</v>
+        <v>1522</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>693162.5</v>
+        <v>840454</v>
       </c>
     </row>
     <row r="202">
@@ -4237,13 +4243,13 @@
         <v>204</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>42.92</v>
+        <v>42.97</v>
       </c>
       <c r="C202" s="2" t="n">
-        <v>52405</v>
+        <v>14083</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>797977</v>
+        <v>693162.5</v>
       </c>
     </row>
     <row r="203">
@@ -4251,13 +4257,13 @@
         <v>205</v>
       </c>
       <c r="B203" s="2" t="n">
-        <v>42.85</v>
+        <v>42.92</v>
       </c>
       <c r="C203" s="2" t="n">
-        <v>13629</v>
+        <v>52405</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>750960</v>
+        <v>797977</v>
       </c>
     </row>
     <row r="204">
@@ -4265,13 +4271,13 @@
         <v>206</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>42.75</v>
+        <v>42.85</v>
       </c>
       <c r="C204" s="2" t="n">
-        <v>464724</v>
+        <v>13629</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>1041709.5</v>
+        <v>750960</v>
       </c>
     </row>
     <row r="205">
@@ -4279,13 +4285,13 @@
         <v>207</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>42.73</v>
+        <v>42.75</v>
       </c>
       <c r="C205" s="2" t="n">
-        <v>16559</v>
+        <v>464724</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>766130</v>
+        <v>1041709.5</v>
       </c>
     </row>
     <row r="206">
@@ -4293,13 +4299,13 @@
         <v>208</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>42.68</v>
+        <v>42.73</v>
       </c>
       <c r="C206" s="2" t="n">
-        <v>30387</v>
+        <v>16559</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>675000</v>
+        <v>766130</v>
       </c>
     </row>
     <row r="207">
@@ -4307,13 +4313,13 @@
         <v>209</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>42.65</v>
+        <v>42.68</v>
       </c>
       <c r="C207" s="2" t="n">
-        <v>34225</v>
+        <v>30387</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>718785</v>
+        <v>675000</v>
       </c>
     </row>
     <row r="208">
@@ -4324,10 +4330,10 @@
         <v>42.65</v>
       </c>
       <c r="C208" s="2" t="n">
-        <v>21768</v>
+        <v>34225</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>846800</v>
+        <v>718785</v>
       </c>
     </row>
     <row r="209">
@@ -4335,13 +4341,13 @@
         <v>211</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>42.64</v>
+        <v>42.65</v>
       </c>
       <c r="C209" s="2" t="n">
-        <v>8539</v>
+        <v>21768</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>770838</v>
+        <v>846800</v>
       </c>
     </row>
     <row r="210">
@@ -4349,13 +4355,13 @@
         <v>212</v>
       </c>
       <c r="B210" s="2" t="n">
-        <v>42.63</v>
+        <v>42.64</v>
       </c>
       <c r="C210" s="2" t="n">
-        <v>10755</v>
+        <v>8539</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>701107</v>
+        <v>770838</v>
       </c>
     </row>
     <row r="211">
@@ -4363,13 +4369,13 @@
         <v>213</v>
       </c>
       <c r="B211" s="2" t="n">
-        <v>42.61</v>
+        <v>42.63</v>
       </c>
       <c r="C211" s="2" t="n">
-        <v>15355</v>
+        <v>10755</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>665057</v>
+        <v>701107</v>
       </c>
     </row>
     <row r="212">
@@ -4377,13 +4383,13 @@
         <v>214</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>42.6</v>
+        <v>42.61</v>
       </c>
       <c r="C212" s="2" t="n">
-        <v>22383</v>
+        <v>15355</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>781954</v>
+        <v>665057</v>
       </c>
     </row>
     <row r="213">
@@ -4391,13 +4397,13 @@
         <v>215</v>
       </c>
       <c r="B213" s="2" t="n">
-        <v>42.58</v>
+        <v>42.6</v>
       </c>
       <c r="C213" s="2" t="n">
-        <v>26816</v>
+        <v>22383</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>1039083</v>
+        <v>781954</v>
       </c>
     </row>
     <row r="214">
@@ -4408,10 +4414,10 @@
         <v>42.58</v>
       </c>
       <c r="C214" s="2" t="n">
-        <v>39598</v>
+        <v>26816</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>680666.5</v>
+        <v>1039083</v>
       </c>
     </row>
     <row r="215">
@@ -4419,13 +4425,13 @@
         <v>217</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>42.54</v>
+        <v>42.58</v>
       </c>
       <c r="C215" s="2" t="n">
-        <v>12893</v>
+        <v>39598</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>726862</v>
+        <v>680666.5</v>
       </c>
     </row>
     <row r="216">
@@ -4433,13 +4439,13 @@
         <v>218</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>42.46</v>
+        <v>42.54</v>
       </c>
       <c r="C216" s="2" t="n">
-        <v>38274</v>
+        <v>12893</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>668024</v>
+        <v>726862</v>
       </c>
     </row>
     <row r="217">
@@ -4447,13 +4453,13 @@
         <v>219</v>
       </c>
       <c r="B217" s="2" t="n">
-        <v>42.45</v>
+        <v>42.46</v>
       </c>
       <c r="C217" s="2" t="n">
-        <v>7409</v>
+        <v>38274</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>1041101.5</v>
+        <v>668024</v>
       </c>
     </row>
     <row r="218">
@@ -4461,13 +4467,13 @@
         <v>220</v>
       </c>
       <c r="B218" s="2" t="n">
-        <v>42.43</v>
+        <v>42.45</v>
       </c>
       <c r="C218" s="2" t="n">
-        <v>12788</v>
+        <v>7409</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>1090681</v>
+        <v>1041101.5</v>
       </c>
     </row>
     <row r="219">
@@ -4475,13 +4481,13 @@
         <v>221</v>
       </c>
       <c r="B219" s="2" t="n">
-        <v>42.42</v>
+        <v>42.43</v>
       </c>
       <c r="C219" s="2" t="n">
-        <v>3808</v>
+        <v>12788</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>625000</v>
+        <v>1090681</v>
       </c>
     </row>
     <row r="220">
@@ -4489,10 +4495,10 @@
         <v>222</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>42.38</v>
+        <v>42.42</v>
       </c>
       <c r="C220" s="2" t="n">
-        <v>11704</v>
+        <v>3808</v>
       </c>
       <c r="D220" s="2" t="n">
         <v>625000</v>
@@ -4503,13 +4509,13 @@
         <v>223</v>
       </c>
       <c r="B221" s="2" t="n">
-        <v>42.35</v>
+        <v>42.38</v>
       </c>
       <c r="C221" s="2" t="n">
-        <v>4986</v>
+        <v>11704</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>733740</v>
+        <v>625000</v>
       </c>
     </row>
     <row r="222">
@@ -4517,13 +4523,13 @@
         <v>224</v>
       </c>
       <c r="B222" s="2" t="n">
-        <v>42.34</v>
+        <v>42.35</v>
       </c>
       <c r="C222" s="2" t="n">
-        <v>50566</v>
+        <v>4986</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>729219</v>
+        <v>733740</v>
       </c>
     </row>
     <row r="223">
@@ -4531,13 +4537,13 @@
         <v>225</v>
       </c>
       <c r="B223" s="2" t="n">
-        <v>42.33</v>
+        <v>42.34</v>
       </c>
       <c r="C223" s="2" t="n">
-        <v>18408</v>
+        <v>50566</v>
       </c>
       <c r="D223" s="2" t="n">
-        <v>686129</v>
+        <v>729219</v>
       </c>
     </row>
     <row r="224">
@@ -4545,13 +4551,13 @@
         <v>226</v>
       </c>
       <c r="B224" s="2" t="n">
-        <v>42.27</v>
+        <v>42.33</v>
       </c>
       <c r="C224" s="2" t="n">
-        <v>8515</v>
+        <v>18408</v>
       </c>
       <c r="D224" s="2" t="n">
-        <v>763910</v>
+        <v>686129</v>
       </c>
     </row>
     <row r="225">
@@ -4559,13 +4565,13 @@
         <v>227</v>
       </c>
       <c r="B225" s="2" t="n">
-        <v>42.26</v>
+        <v>42.27</v>
       </c>
       <c r="C225" s="2" t="n">
-        <v>17406</v>
+        <v>8515</v>
       </c>
       <c r="D225" s="2" t="n">
-        <v>642084</v>
+        <v>763910</v>
       </c>
     </row>
     <row r="226">
@@ -4573,13 +4579,13 @@
         <v>228</v>
       </c>
       <c r="B226" s="2" t="n">
-        <v>42.14</v>
+        <v>42.26</v>
       </c>
       <c r="C226" s="2" t="n">
-        <v>23890</v>
+        <v>17406</v>
       </c>
       <c r="D226" s="2" t="n">
-        <v>784078</v>
+        <v>642084</v>
       </c>
     </row>
     <row r="227">
@@ -4587,13 +4593,13 @@
         <v>229</v>
       </c>
       <c r="B227" s="2" t="n">
-        <v>42.12</v>
+        <v>42.14</v>
       </c>
       <c r="C227" s="2" t="n">
-        <v>16459</v>
+        <v>23890</v>
       </c>
       <c r="D227" s="2" t="n">
-        <v>738395.5</v>
+        <v>784078</v>
       </c>
     </row>
     <row r="228">
@@ -4601,13 +4607,13 @@
         <v>230</v>
       </c>
       <c r="B228" s="2" t="n">
-        <v>42.09</v>
+        <v>42.12</v>
       </c>
       <c r="C228" s="2" t="n">
-        <v>27659</v>
+        <v>16459</v>
       </c>
       <c r="D228" s="2" t="n">
-        <v>736132.5</v>
+        <v>738395.5</v>
       </c>
     </row>
     <row r="229">
@@ -4615,13 +4621,13 @@
         <v>231</v>
       </c>
       <c r="B229" s="2" t="n">
-        <v>42.02</v>
+        <v>42.09</v>
       </c>
       <c r="C229" s="2" t="n">
-        <v>10517</v>
+        <v>27659</v>
       </c>
       <c r="D229" s="2" t="n">
-        <v>775000</v>
+        <v>736132.5</v>
       </c>
     </row>
     <row r="230">
@@ -4629,13 +4635,13 @@
         <v>232</v>
       </c>
       <c r="B230" s="2" t="n">
-        <v>41.82</v>
+        <v>42.02</v>
       </c>
       <c r="C230" s="2" t="n">
-        <v>10882</v>
+        <v>10517</v>
       </c>
       <c r="D230" s="2" t="n">
-        <v>837500</v>
+        <v>775000</v>
       </c>
     </row>
     <row r="231">
@@ -4643,13 +4649,13 @@
         <v>233</v>
       </c>
       <c r="B231" s="2" t="n">
-        <v>41.78</v>
+        <v>41.82</v>
       </c>
       <c r="C231" s="2" t="n">
-        <v>14647</v>
+        <v>10882</v>
       </c>
       <c r="D231" s="2" t="n">
-        <v>710610</v>
+        <v>837500</v>
       </c>
     </row>
     <row r="232">
@@ -4657,13 +4663,13 @@
         <v>234</v>
       </c>
       <c r="B232" s="2" t="n">
-        <v>41.77</v>
+        <v>41.78</v>
       </c>
       <c r="C232" s="2" t="n">
-        <v>122709</v>
+        <v>14647</v>
       </c>
       <c r="D232" s="2" t="n">
-        <v>790720</v>
+        <v>710610</v>
       </c>
     </row>
     <row r="233">
@@ -4671,13 +4677,13 @@
         <v>235</v>
       </c>
       <c r="B233" s="2" t="n">
-        <v>41.73</v>
+        <v>41.77</v>
       </c>
       <c r="C233" s="2" t="n">
-        <v>103193</v>
+        <v>122709</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>796960</v>
+        <v>790720</v>
       </c>
     </row>
     <row r="234">
@@ -4685,13 +4691,13 @@
         <v>236</v>
       </c>
       <c r="B234" s="2" t="n">
-        <v>41.72</v>
+        <v>41.74</v>
       </c>
       <c r="C234" s="2" t="n">
-        <v>29138</v>
+        <v>5563</v>
       </c>
       <c r="D234" s="2" t="n">
-        <v>764707</v>
+        <v>700568</v>
       </c>
     </row>
     <row r="235">
@@ -4699,13 +4705,13 @@
         <v>237</v>
       </c>
       <c r="B235" s="2" t="n">
-        <v>41.66</v>
+        <v>41.73</v>
       </c>
       <c r="C235" s="2" t="n">
-        <v>15224</v>
+        <v>103193</v>
       </c>
       <c r="D235" s="2" t="n">
-        <v>703513.5</v>
+        <v>796960</v>
       </c>
     </row>
     <row r="236">
@@ -4713,13 +4719,13 @@
         <v>238</v>
       </c>
       <c r="B236" s="2" t="n">
-        <v>41.61</v>
+        <v>41.72</v>
       </c>
       <c r="C236" s="2" t="n">
-        <v>40422</v>
+        <v>29138</v>
       </c>
       <c r="D236" s="2" t="n">
-        <v>824531</v>
+        <v>764707</v>
       </c>
     </row>
     <row r="237">
@@ -4727,13 +4733,13 @@
         <v>239</v>
       </c>
       <c r="B237" s="2" t="n">
-        <v>41.6</v>
+        <v>41.66</v>
       </c>
       <c r="C237" s="2" t="n">
-        <v>3038</v>
+        <v>15224</v>
       </c>
       <c r="D237" s="2" t="n">
-        <v>904680</v>
+        <v>703513.5</v>
       </c>
     </row>
     <row r="238">
@@ -4741,13 +4747,13 @@
         <v>240</v>
       </c>
       <c r="B238" s="2" t="n">
-        <v>41.57</v>
+        <v>41.61</v>
       </c>
       <c r="C238" s="2" t="n">
-        <v>11065</v>
+        <v>40422</v>
       </c>
       <c r="D238" s="2" t="n">
-        <v>685462</v>
+        <v>824531</v>
       </c>
     </row>
     <row r="239">
@@ -4755,13 +4761,13 @@
         <v>241</v>
       </c>
       <c r="B239" s="2" t="n">
-        <v>41.57</v>
+        <v>41.6</v>
       </c>
       <c r="C239" s="2" t="n">
-        <v>16268</v>
+        <v>3038</v>
       </c>
       <c r="D239" s="2" t="n">
-        <v>648509</v>
+        <v>904680</v>
       </c>
     </row>
     <row r="240">
@@ -4769,13 +4775,13 @@
         <v>242</v>
       </c>
       <c r="B240" s="2" t="n">
-        <v>41.55</v>
+        <v>41.57</v>
       </c>
       <c r="C240" s="2" t="n">
-        <v>159398</v>
+        <v>11065</v>
       </c>
       <c r="D240" s="2" t="n">
-        <v>787016</v>
+        <v>685462</v>
       </c>
     </row>
     <row r="241">
@@ -4783,13 +4789,13 @@
         <v>243</v>
       </c>
       <c r="B241" s="2" t="n">
-        <v>41.51</v>
+        <v>41.57</v>
       </c>
       <c r="C241" s="2" t="n">
-        <v>32679</v>
+        <v>16268</v>
       </c>
       <c r="D241" s="2" t="n">
-        <v>772440</v>
+        <v>648509</v>
       </c>
     </row>
     <row r="242">
@@ -4797,13 +4803,13 @@
         <v>244</v>
       </c>
       <c r="B242" s="2" t="n">
-        <v>41.46</v>
+        <v>41.55</v>
       </c>
       <c r="C242" s="2" t="n">
-        <v>7805</v>
+        <v>159398</v>
       </c>
       <c r="D242" s="2" t="n">
-        <v>648438</v>
+        <v>787016</v>
       </c>
     </row>
     <row r="243">
@@ -4811,13 +4817,13 @@
         <v>245</v>
       </c>
       <c r="B243" s="2" t="n">
-        <v>41.44</v>
+        <v>41.51</v>
       </c>
       <c r="C243" s="2" t="n">
-        <v>26646</v>
+        <v>32679</v>
       </c>
       <c r="D243" s="2" t="n">
-        <v>840000</v>
+        <v>772440</v>
       </c>
     </row>
     <row r="244">
@@ -4825,13 +4831,13 @@
         <v>246</v>
       </c>
       <c r="B244" s="2" t="n">
-        <v>41.44</v>
+        <v>41.46</v>
       </c>
       <c r="C244" s="2" t="n">
-        <v>22845</v>
+        <v>7805</v>
       </c>
       <c r="D244" s="2" t="n">
-        <v>675824.5</v>
+        <v>648438</v>
       </c>
     </row>
     <row r="245">
@@ -4839,13 +4845,13 @@
         <v>247</v>
       </c>
       <c r="B245" s="2" t="n">
-        <v>41.27</v>
+        <v>41.44</v>
       </c>
       <c r="C245" s="2" t="n">
-        <v>23311</v>
+        <v>26646</v>
       </c>
       <c r="D245" s="2" t="n">
-        <v>1043083.5</v>
+        <v>840000</v>
       </c>
     </row>
     <row r="246">
@@ -4853,13 +4859,13 @@
         <v>248</v>
       </c>
       <c r="B246" s="2" t="n">
-        <v>41.24</v>
+        <v>41.44</v>
       </c>
       <c r="C246" s="2" t="n">
-        <v>21115</v>
+        <v>22845</v>
       </c>
       <c r="D246" s="2" t="n">
-        <v>679435</v>
+        <v>675824.5</v>
       </c>
     </row>
     <row r="247">
@@ -4867,13 +4873,13 @@
         <v>249</v>
       </c>
       <c r="B247" s="2" t="n">
-        <v>41.2</v>
+        <v>41.27</v>
       </c>
       <c r="C247" s="2" t="n">
-        <v>12673</v>
+        <v>23311</v>
       </c>
       <c r="D247" s="2" t="n">
-        <v>735745</v>
+        <v>1043083.5</v>
       </c>
     </row>
     <row r="248">
@@ -4881,13 +4887,13 @@
         <v>250</v>
       </c>
       <c r="B248" s="2" t="n">
-        <v>41.17</v>
+        <v>41.24</v>
       </c>
       <c r="C248" s="2" t="n">
-        <v>6124</v>
+        <v>21115</v>
       </c>
       <c r="D248" s="2" t="n">
-        <v>843394.5</v>
+        <v>679435</v>
       </c>
     </row>
     <row r="249">
@@ -4895,13 +4901,13 @@
         <v>251</v>
       </c>
       <c r="B249" s="2" t="n">
-        <v>41.08</v>
+        <v>41.2</v>
       </c>
       <c r="C249" s="2" t="n">
-        <v>8484</v>
+        <v>12673</v>
       </c>
       <c r="D249" s="2" t="n">
-        <v>848509</v>
+        <v>735745</v>
       </c>
     </row>
     <row r="250">
@@ -4909,13 +4915,13 @@
         <v>252</v>
       </c>
       <c r="B250" s="2" t="n">
-        <v>41.07</v>
+        <v>41.17</v>
       </c>
       <c r="C250" s="2" t="n">
-        <v>20971</v>
+        <v>6124</v>
       </c>
       <c r="D250" s="2" t="n">
-        <v>730100</v>
+        <v>843394.5</v>
       </c>
     </row>
     <row r="251">
@@ -4923,13 +4929,13 @@
         <v>253</v>
       </c>
       <c r="B251" s="2" t="n">
-        <v>41.07</v>
+        <v>41.08</v>
       </c>
       <c r="C251" s="2" t="n">
-        <v>13691</v>
+        <v>8484</v>
       </c>
       <c r="D251" s="2" t="n">
-        <v>725200</v>
+        <v>848509</v>
       </c>
     </row>
     <row r="252">
@@ -4937,13 +4943,13 @@
         <v>254</v>
       </c>
       <c r="B252" s="2" t="n">
-        <v>40.99</v>
+        <v>41.07</v>
       </c>
       <c r="C252" s="2" t="n">
-        <v>28516</v>
+        <v>20971</v>
       </c>
       <c r="D252" s="2" t="n">
-        <v>701570</v>
+        <v>730100</v>
       </c>
     </row>
     <row r="253">
@@ -4951,13 +4957,13 @@
         <v>255</v>
       </c>
       <c r="B253" s="2" t="n">
-        <v>40.97</v>
+        <v>41.07</v>
       </c>
       <c r="C253" s="2" t="n">
-        <v>9575</v>
+        <v>13691</v>
       </c>
       <c r="D253" s="2" t="n">
-        <v>701105</v>
+        <v>725200</v>
       </c>
     </row>
     <row r="254">
@@ -4965,13 +4971,13 @@
         <v>256</v>
       </c>
       <c r="B254" s="2" t="n">
-        <v>40.94</v>
+        <v>40.99</v>
       </c>
       <c r="C254" s="2" t="n">
-        <v>5470</v>
+        <v>28516</v>
       </c>
       <c r="D254" s="2" t="n">
-        <v>812386</v>
+        <v>701570</v>
       </c>
     </row>
     <row r="255">
@@ -4979,13 +4985,13 @@
         <v>257</v>
       </c>
       <c r="B255" s="2" t="n">
-        <v>40.93</v>
+        <v>40.97</v>
       </c>
       <c r="C255" s="2" t="n">
-        <v>8301</v>
+        <v>9575</v>
       </c>
       <c r="D255" s="2" t="n">
-        <v>747300</v>
+        <v>701105</v>
       </c>
     </row>
     <row r="256">
@@ -4993,13 +4999,13 @@
         <v>258</v>
       </c>
       <c r="B256" s="2" t="n">
-        <v>40.78</v>
+        <v>40.94</v>
       </c>
       <c r="C256" s="2" t="n">
-        <v>147783</v>
+        <v>5470</v>
       </c>
       <c r="D256" s="2" t="n">
-        <v>817138.5</v>
+        <v>812386</v>
       </c>
     </row>
     <row r="257">
@@ -5007,13 +5013,13 @@
         <v>259</v>
       </c>
       <c r="B257" s="2" t="n">
-        <v>40.67</v>
+        <v>40.93</v>
       </c>
       <c r="C257" s="2" t="n">
-        <v>17839</v>
+        <v>8301</v>
       </c>
       <c r="D257" s="2" t="n">
-        <v>666274</v>
+        <v>747300</v>
       </c>
     </row>
     <row r="258">
@@ -5021,13 +5027,13 @@
         <v>260</v>
       </c>
       <c r="B258" s="2" t="n">
-        <v>40.67</v>
+        <v>40.78</v>
       </c>
       <c r="C258" s="2" t="n">
-        <v>85998</v>
+        <v>147783</v>
       </c>
       <c r="D258" s="2" t="n">
-        <v>758210</v>
+        <v>817138.5</v>
       </c>
     </row>
     <row r="259">
@@ -5038,10 +5044,10 @@
         <v>40.67</v>
       </c>
       <c r="C259" s="2" t="n">
-        <v>12769</v>
+        <v>17839</v>
       </c>
       <c r="D259" s="2" t="n">
-        <v>775000</v>
+        <v>666274</v>
       </c>
     </row>
     <row r="260">
@@ -5049,13 +5055,13 @@
         <v>262</v>
       </c>
       <c r="B260" s="2" t="n">
-        <v>40.63</v>
+        <v>40.67</v>
       </c>
       <c r="C260" s="2" t="n">
-        <v>27227</v>
+        <v>85998</v>
       </c>
       <c r="D260" s="2" t="n">
-        <v>711296</v>
+        <v>758210</v>
       </c>
     </row>
     <row r="261">
@@ -5063,13 +5069,13 @@
         <v>263</v>
       </c>
       <c r="B261" s="2" t="n">
-        <v>40.62</v>
+        <v>40.67</v>
       </c>
       <c r="C261" s="2" t="n">
-        <v>11786</v>
+        <v>12769</v>
       </c>
       <c r="D261" s="2" t="n">
-        <v>801406</v>
+        <v>775000</v>
       </c>
     </row>
     <row r="262">
@@ -5077,13 +5083,13 @@
         <v>264</v>
       </c>
       <c r="B262" s="2" t="n">
-        <v>40.61</v>
+        <v>40.63</v>
       </c>
       <c r="C262" s="2" t="n">
-        <v>41897</v>
+        <v>27227</v>
       </c>
       <c r="D262" s="2" t="n">
-        <v>847214</v>
+        <v>711296</v>
       </c>
     </row>
     <row r="263">
@@ -5091,13 +5097,13 @@
         <v>265</v>
       </c>
       <c r="B263" s="2" t="n">
-        <v>40.56</v>
+        <v>40.62</v>
       </c>
       <c r="C263" s="2" t="n">
-        <v>7396</v>
+        <v>11786</v>
       </c>
       <c r="D263" s="2" t="n">
-        <v>625000</v>
+        <v>801406</v>
       </c>
     </row>
     <row r="264">
@@ -5105,13 +5111,13 @@
         <v>266</v>
       </c>
       <c r="B264" s="2" t="n">
-        <v>40.53</v>
+        <v>40.61</v>
       </c>
       <c r="C264" s="2" t="n">
-        <v>4279</v>
+        <v>41897</v>
       </c>
       <c r="D264" s="2" t="n">
-        <v>964104</v>
+        <v>847214</v>
       </c>
     </row>
     <row r="265">
@@ -5119,13 +5125,13 @@
         <v>267</v>
       </c>
       <c r="B265" s="2" t="n">
-        <v>40.53</v>
+        <v>40.56</v>
       </c>
       <c r="C265" s="2" t="n">
-        <v>22031</v>
+        <v>7396</v>
       </c>
       <c r="D265" s="2" t="n">
-        <v>702212</v>
+        <v>625000</v>
       </c>
     </row>
     <row r="266">
@@ -5133,13 +5139,13 @@
         <v>268</v>
       </c>
       <c r="B266" s="2" t="n">
-        <v>40.52</v>
+        <v>40.53</v>
       </c>
       <c r="C266" s="2" t="n">
-        <v>122175</v>
+        <v>4279</v>
       </c>
       <c r="D266" s="2" t="n">
-        <v>827810</v>
+        <v>964104</v>
       </c>
     </row>
     <row r="267">
@@ -5147,13 +5153,13 @@
         <v>269</v>
       </c>
       <c r="B267" s="2" t="n">
-        <v>40.41</v>
+        <v>40.53</v>
       </c>
       <c r="C267" s="2" t="n">
-        <v>7479</v>
+        <v>22031</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>625000</v>
+        <v>702212</v>
       </c>
     </row>
     <row r="268">
@@ -5161,13 +5167,13 @@
         <v>270</v>
       </c>
       <c r="B268" s="2" t="n">
-        <v>40.39</v>
+        <v>40.52</v>
       </c>
       <c r="C268" s="2" t="n">
-        <v>26151</v>
+        <v>122175</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>764925</v>
+        <v>827810</v>
       </c>
     </row>
     <row r="269">
@@ -5175,13 +5181,13 @@
         <v>271</v>
       </c>
       <c r="B269" s="2" t="n">
-        <v>40.25</v>
+        <v>40.41</v>
       </c>
       <c r="C269" s="2" t="n">
-        <v>42825</v>
+        <v>7479</v>
       </c>
       <c r="D269" s="2" t="n">
-        <v>706188</v>
+        <v>625000</v>
       </c>
     </row>
     <row r="270">
@@ -5189,13 +5195,13 @@
         <v>272</v>
       </c>
       <c r="B270" s="2" t="n">
-        <v>40.17</v>
+        <v>40.39</v>
       </c>
       <c r="C270" s="2" t="n">
-        <v>5925</v>
+        <v>26151</v>
       </c>
       <c r="D270" s="2" t="n">
-        <v>918490</v>
+        <v>764925</v>
       </c>
     </row>
     <row r="271">
@@ -5203,13 +5209,13 @@
         <v>273</v>
       </c>
       <c r="B271" s="2" t="n">
-        <v>40.05</v>
+        <v>40.25</v>
       </c>
       <c r="C271" s="2" t="n">
-        <v>20427</v>
+        <v>42825</v>
       </c>
       <c r="D271" s="2" t="n">
-        <v>695000</v>
+        <v>706188</v>
       </c>
     </row>
     <row r="272">
@@ -5217,13 +5223,13 @@
         <v>274</v>
       </c>
       <c r="B272" s="2" t="n">
-        <v>39.86</v>
+        <v>40.17</v>
       </c>
       <c r="C272" s="2" t="n">
-        <v>23415</v>
+        <v>5925</v>
       </c>
       <c r="D272" s="2" t="n">
-        <v>762187.5</v>
+        <v>918490</v>
       </c>
     </row>
     <row r="273">
@@ -5231,13 +5237,13 @@
         <v>275</v>
       </c>
       <c r="B273" s="2" t="n">
-        <v>39.8</v>
+        <v>40.05</v>
       </c>
       <c r="C273" s="2" t="n">
-        <v>172756</v>
+        <v>20427</v>
       </c>
       <c r="D273" s="2" t="n">
-        <v>834435</v>
+        <v>695000</v>
       </c>
     </row>
     <row r="274">
@@ -5245,13 +5251,13 @@
         <v>276</v>
       </c>
       <c r="B274" s="2" t="n">
-        <v>39.56</v>
+        <v>39.86</v>
       </c>
       <c r="C274" s="2" t="n">
-        <v>3492</v>
+        <v>23415</v>
       </c>
       <c r="D274" s="2" t="n">
-        <v>876500</v>
+        <v>762187.5</v>
       </c>
     </row>
     <row r="275">
@@ -5259,13 +5265,13 @@
         <v>277</v>
       </c>
       <c r="B275" s="2" t="n">
-        <v>39.56</v>
+        <v>39.8</v>
       </c>
       <c r="C275" s="2" t="n">
-        <v>4668</v>
+        <v>172756</v>
       </c>
       <c r="D275" s="2" t="n">
-        <v>726455</v>
+        <v>834435</v>
       </c>
     </row>
     <row r="276">
@@ -5273,13 +5279,13 @@
         <v>278</v>
       </c>
       <c r="B276" s="2" t="n">
-        <v>39.47</v>
+        <v>39.56</v>
       </c>
       <c r="C276" s="2" t="n">
-        <v>15085</v>
+        <v>3492</v>
       </c>
       <c r="D276" s="2" t="n">
-        <v>642791</v>
+        <v>876500</v>
       </c>
     </row>
     <row r="277">
@@ -5287,13 +5293,13 @@
         <v>279</v>
       </c>
       <c r="B277" s="2" t="n">
-        <v>39.44</v>
+        <v>39.56</v>
       </c>
       <c r="C277" s="2" t="n">
-        <v>24731</v>
+        <v>4668</v>
       </c>
       <c r="D277" s="2" t="n">
-        <v>781044</v>
+        <v>726455</v>
       </c>
     </row>
     <row r="278">
@@ -5301,13 +5307,13 @@
         <v>280</v>
       </c>
       <c r="B278" s="2" t="n">
-        <v>39.32</v>
+        <v>39.47</v>
       </c>
       <c r="C278" s="2" t="n">
-        <v>32780</v>
+        <v>15085</v>
       </c>
       <c r="D278" s="2" t="n">
-        <v>769128</v>
+        <v>642791</v>
       </c>
     </row>
     <row r="279">
@@ -5315,13 +5321,13 @@
         <v>281</v>
       </c>
       <c r="B279" s="2" t="n">
-        <v>39.29</v>
+        <v>39.44</v>
       </c>
       <c r="C279" s="2" t="n">
-        <v>33419</v>
+        <v>24731</v>
       </c>
       <c r="D279" s="2" t="n">
-        <v>791677.5</v>
+        <v>781044</v>
       </c>
     </row>
     <row r="280">
@@ -5329,13 +5335,13 @@
         <v>282</v>
       </c>
       <c r="B280" s="2" t="n">
-        <v>39.29</v>
+        <v>39.32</v>
       </c>
       <c r="C280" s="2" t="n">
-        <v>21688</v>
+        <v>32780</v>
       </c>
       <c r="D280" s="2" t="n">
-        <v>813510</v>
+        <v>769128</v>
       </c>
     </row>
     <row r="281">
@@ -5343,13 +5349,13 @@
         <v>283</v>
       </c>
       <c r="B281" s="2" t="n">
-        <v>39.27</v>
+        <v>39.29</v>
       </c>
       <c r="C281" s="2" t="n">
-        <v>5489</v>
+        <v>33419</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>825238.5</v>
+        <v>791677.5</v>
       </c>
     </row>
     <row r="282">
@@ -5357,13 +5363,13 @@
         <v>284</v>
       </c>
       <c r="B282" s="2" t="n">
-        <v>39.12</v>
+        <v>39.29</v>
       </c>
       <c r="C282" s="2" t="n">
-        <v>12083</v>
+        <v>21688</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>962083</v>
+        <v>813510</v>
       </c>
     </row>
     <row r="283">
@@ -5371,13 +5377,13 @@
         <v>285</v>
       </c>
       <c r="B283" s="2" t="n">
-        <v>39.08</v>
+        <v>39.27</v>
       </c>
       <c r="C283" s="2" t="n">
-        <v>12239</v>
+        <v>5489</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>989379</v>
+        <v>825238.5</v>
       </c>
     </row>
     <row r="284">
@@ -5385,13 +5391,13 @@
         <v>286</v>
       </c>
       <c r="B284" s="2" t="n">
-        <v>39.07</v>
+        <v>39.12</v>
       </c>
       <c r="C284" s="2" t="n">
-        <v>137131</v>
+        <v>12083</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>754290</v>
+        <v>962083</v>
       </c>
     </row>
     <row r="285">
@@ -5399,13 +5405,13 @@
         <v>287</v>
       </c>
       <c r="B285" s="2" t="n">
-        <v>38.98</v>
+        <v>39.08</v>
       </c>
       <c r="C285" s="2" t="n">
-        <v>22855</v>
+        <v>12239</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>737577</v>
+        <v>989379</v>
       </c>
     </row>
     <row r="286">
@@ -5413,13 +5419,13 @@
         <v>288</v>
       </c>
       <c r="B286" s="2" t="n">
-        <v>38.97</v>
+        <v>39.07</v>
       </c>
       <c r="C286" s="2" t="n">
-        <v>1424</v>
+        <v>137131</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>862502</v>
+        <v>754290</v>
       </c>
     </row>
     <row r="287">
@@ -5427,13 +5433,13 @@
         <v>289</v>
       </c>
       <c r="B287" s="2" t="n">
-        <v>38.97</v>
+        <v>38.98</v>
       </c>
       <c r="C287" s="2" t="n">
-        <v>15164</v>
+        <v>22855</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>730665</v>
+        <v>737577</v>
       </c>
     </row>
     <row r="288">
@@ -5441,13 +5447,13 @@
         <v>290</v>
       </c>
       <c r="B288" s="2" t="n">
-        <v>38.93</v>
+        <v>38.97</v>
       </c>
       <c r="C288" s="2" t="n">
-        <v>47900</v>
+        <v>1424</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>862500</v>
+        <v>862502</v>
       </c>
     </row>
     <row r="289">
@@ -5455,13 +5461,13 @@
         <v>291</v>
       </c>
       <c r="B289" s="2" t="n">
-        <v>38.81</v>
+        <v>38.97</v>
       </c>
       <c r="C289" s="2" t="n">
-        <v>14656</v>
+        <v>15164</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>650164</v>
+        <v>730665</v>
       </c>
     </row>
     <row r="290">
@@ -5469,13 +5475,13 @@
         <v>292</v>
       </c>
       <c r="B290" s="2" t="n">
-        <v>38.74</v>
+        <v>38.93</v>
       </c>
       <c r="C290" s="2" t="n">
-        <v>17412</v>
+        <v>47900</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>849468</v>
+        <v>862500</v>
       </c>
     </row>
     <row r="291">
@@ -5483,13 +5489,13 @@
         <v>293</v>
       </c>
       <c r="B291" s="2" t="n">
-        <v>38.71</v>
+        <v>38.81</v>
       </c>
       <c r="C291" s="2" t="n">
-        <v>19319</v>
+        <v>14656</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>736100</v>
+        <v>650164</v>
       </c>
     </row>
     <row r="292">
@@ -5497,13 +5503,13 @@
         <v>294</v>
       </c>
       <c r="B292" s="2" t="n">
-        <v>38.7</v>
+        <v>38.74</v>
       </c>
       <c r="C292" s="2" t="n">
-        <v>39260</v>
+        <v>17412</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>735750</v>
+        <v>849468</v>
       </c>
     </row>
     <row r="293">
@@ -5511,13 +5517,13 @@
         <v>295</v>
       </c>
       <c r="B293" s="2" t="n">
-        <v>38.48</v>
+        <v>38.71</v>
       </c>
       <c r="C293" s="2" t="n">
-        <v>30895</v>
+        <v>19319</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>685728</v>
+        <v>736100</v>
       </c>
     </row>
     <row r="294">
@@ -5525,13 +5531,13 @@
         <v>296</v>
       </c>
       <c r="B294" s="2" t="n">
-        <v>38.47</v>
+        <v>38.7</v>
       </c>
       <c r="C294" s="2" t="n">
-        <v>139724</v>
+        <v>39260</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>879350</v>
+        <v>735750</v>
       </c>
     </row>
     <row r="295">
@@ -5539,13 +5545,13 @@
         <v>297</v>
       </c>
       <c r="B295" s="2" t="n">
-        <v>38.2</v>
+        <v>38.48</v>
       </c>
       <c r="C295" s="2" t="n">
-        <v>8966</v>
+        <v>30895</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>698241</v>
+        <v>685728</v>
       </c>
     </row>
     <row r="296">
@@ -5553,13 +5559,13 @@
         <v>298</v>
       </c>
       <c r="B296" s="2" t="n">
-        <v>38.16</v>
+        <v>38.47</v>
       </c>
       <c r="C296" s="2" t="n">
-        <v>8602</v>
+        <v>139724</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>787393</v>
+        <v>879350</v>
       </c>
     </row>
     <row r="297">
@@ -5567,13 +5573,13 @@
         <v>299</v>
       </c>
       <c r="B297" s="2" t="n">
-        <v>38.04</v>
+        <v>38.2</v>
       </c>
       <c r="C297" s="2" t="n">
-        <v>6855</v>
+        <v>8966</v>
       </c>
       <c r="D297" s="2" t="n">
-        <v>724150</v>
+        <v>698241</v>
       </c>
     </row>
     <row r="298">
@@ -5581,13 +5587,13 @@
         <v>300</v>
       </c>
       <c r="B298" s="2" t="n">
-        <v>37.94</v>
+        <v>38.16</v>
       </c>
       <c r="C298" s="2" t="n">
-        <v>4526</v>
+        <v>8602</v>
       </c>
       <c r="D298" s="2" t="n">
-        <v>885213</v>
+        <v>787393</v>
       </c>
     </row>
     <row r="299">
@@ -5595,13 +5601,13 @@
         <v>301</v>
       </c>
       <c r="B299" s="2" t="n">
-        <v>37.83</v>
+        <v>38.04</v>
       </c>
       <c r="C299" s="2" t="n">
-        <v>8524</v>
+        <v>6855</v>
       </c>
       <c r="D299" s="2" t="n">
-        <v>950812</v>
+        <v>724150</v>
       </c>
     </row>
     <row r="300">
@@ -5609,13 +5615,13 @@
         <v>302</v>
       </c>
       <c r="B300" s="2" t="n">
-        <v>37.41</v>
+        <v>37.94</v>
       </c>
       <c r="C300" s="2" t="n">
-        <v>28041</v>
+        <v>4526</v>
       </c>
       <c r="D300" s="2" t="n">
-        <v>737562</v>
+        <v>885213</v>
       </c>
     </row>
     <row r="301">
@@ -5623,13 +5629,13 @@
         <v>303</v>
       </c>
       <c r="B301" s="2" t="n">
-        <v>37.36</v>
+        <v>37.83</v>
       </c>
       <c r="C301" s="2" t="n">
-        <v>9749</v>
+        <v>8524</v>
       </c>
       <c r="D301" s="2" t="n">
-        <v>673611</v>
+        <v>950812</v>
       </c>
     </row>
     <row r="302">
@@ -5637,13 +5643,13 @@
         <v>304</v>
       </c>
       <c r="B302" s="2" t="n">
-        <v>37.33</v>
+        <v>37.41</v>
       </c>
       <c r="C302" s="2" t="n">
-        <v>100227</v>
+        <v>28041</v>
       </c>
       <c r="D302" s="2" t="n">
-        <v>756734.5</v>
+        <v>737562</v>
       </c>
     </row>
     <row r="303">
@@ -5651,13 +5657,13 @@
         <v>305</v>
       </c>
       <c r="B303" s="2" t="n">
-        <v>37.23</v>
+        <v>37.36</v>
       </c>
       <c r="C303" s="2" t="n">
-        <v>38781</v>
+        <v>9749</v>
       </c>
       <c r="D303" s="2" t="n">
-        <v>906409.5</v>
+        <v>673611</v>
       </c>
     </row>
     <row r="304">
@@ -5665,13 +5671,13 @@
         <v>306</v>
       </c>
       <c r="B304" s="2" t="n">
-        <v>37.13</v>
+        <v>37.33</v>
       </c>
       <c r="C304" s="2" t="n">
-        <v>1993</v>
+        <v>100227</v>
       </c>
       <c r="D304" s="2" t="n">
-        <v>1164641</v>
+        <v>756734.5</v>
       </c>
     </row>
     <row r="305">
@@ -5679,13 +5685,13 @@
         <v>307</v>
       </c>
       <c r="B305" s="2" t="n">
-        <v>37.07</v>
+        <v>37.23</v>
       </c>
       <c r="C305" s="2" t="n">
-        <v>8608</v>
+        <v>38781</v>
       </c>
       <c r="D305" s="2" t="n">
-        <v>690001</v>
+        <v>906409.5</v>
       </c>
     </row>
     <row r="306">
@@ -5693,13 +5699,13 @@
         <v>308</v>
       </c>
       <c r="B306" s="2" t="n">
-        <v>36.88</v>
+        <v>37.13</v>
       </c>
       <c r="C306" s="2" t="n">
-        <v>179328</v>
+        <v>1993</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>723323</v>
+        <v>1164641</v>
       </c>
     </row>
     <row r="307">
@@ -5707,13 +5713,13 @@
         <v>309</v>
       </c>
       <c r="B307" s="2" t="n">
-        <v>36.83</v>
+        <v>37.07</v>
       </c>
       <c r="C307" s="2" t="n">
-        <v>8810</v>
+        <v>8608</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>1052917</v>
+        <v>690001</v>
       </c>
     </row>
     <row r="308">
@@ -5721,13 +5727,13 @@
         <v>310</v>
       </c>
       <c r="B308" s="2" t="n">
-        <v>36.29</v>
+        <v>36.88</v>
       </c>
       <c r="C308" s="2" t="n">
-        <v>29278</v>
+        <v>179328</v>
       </c>
       <c r="D308" s="2" t="n">
-        <v>969705</v>
+        <v>723323</v>
       </c>
     </row>
     <row r="309">
@@ -5735,13 +5741,13 @@
         <v>311</v>
       </c>
       <c r="B309" s="2" t="n">
-        <v>35.94</v>
+        <v>36.83</v>
       </c>
       <c r="C309" s="2" t="n">
-        <v>14330</v>
+        <v>8810</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>625000</v>
+        <v>1052917</v>
       </c>
     </row>
     <row r="310">
@@ -5749,13 +5755,13 @@
         <v>312</v>
       </c>
       <c r="B310" s="2" t="n">
-        <v>35.85</v>
+        <v>36.29</v>
       </c>
       <c r="C310" s="2" t="n">
-        <v>4183</v>
+        <v>29278</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>867422.5</v>
+        <v>969705</v>
       </c>
     </row>
     <row r="311">
@@ -5763,13 +5769,13 @@
         <v>313</v>
       </c>
       <c r="B311" s="2" t="n">
-        <v>35.63</v>
+        <v>35.94</v>
       </c>
       <c r="C311" s="2" t="n">
-        <v>17302</v>
+        <v>14330</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>819840</v>
+        <v>625000</v>
       </c>
     </row>
     <row r="312">
@@ -5777,13 +5783,13 @@
         <v>314</v>
       </c>
       <c r="B312" s="2" t="n">
-        <v>35.41</v>
+        <v>35.85</v>
       </c>
       <c r="C312" s="2" t="n">
-        <v>16739</v>
+        <v>4183</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>831210</v>
+        <v>867422.5</v>
       </c>
     </row>
     <row r="313">
@@ -5791,13 +5797,13 @@
         <v>315</v>
       </c>
       <c r="B313" s="2" t="n">
-        <v>35.4</v>
+        <v>35.63</v>
       </c>
       <c r="C313" s="2" t="n">
-        <v>28335</v>
+        <v>17302</v>
       </c>
       <c r="D313" s="2" t="n">
-        <v>729450</v>
+        <v>819840</v>
       </c>
     </row>
     <row r="314">
@@ -5805,13 +5811,13 @@
         <v>316</v>
       </c>
       <c r="B314" s="2" t="n">
-        <v>35.33</v>
+        <v>35.41</v>
       </c>
       <c r="C314" s="2" t="n">
-        <v>9910</v>
+        <v>16739</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>704458</v>
+        <v>831210</v>
       </c>
     </row>
     <row r="315">
@@ -5819,13 +5825,13 @@
         <v>317</v>
       </c>
       <c r="B315" s="2" t="n">
-        <v>34.5</v>
+        <v>35.4</v>
       </c>
       <c r="C315" s="2" t="n">
-        <v>17815</v>
+        <v>28335</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>1102080</v>
+        <v>729450</v>
       </c>
     </row>
     <row r="316">
@@ -5833,13 +5839,13 @@
         <v>318</v>
       </c>
       <c r="B316" s="2" t="n">
-        <v>34.23</v>
+        <v>35.33</v>
       </c>
       <c r="C316" s="2" t="n">
-        <v>13364</v>
+        <v>9910</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>939655</v>
+        <v>704458</v>
       </c>
     </row>
     <row r="317">
@@ -5847,13 +5853,13 @@
         <v>319</v>
       </c>
       <c r="B317" s="2" t="n">
-        <v>34.14</v>
+        <v>34.5</v>
       </c>
       <c r="C317" s="2" t="n">
-        <v>12432</v>
+        <v>17815</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>672043</v>
+        <v>1102080</v>
       </c>
     </row>
     <row r="318">
@@ -5861,13 +5867,13 @@
         <v>320</v>
       </c>
       <c r="B318" s="2" t="n">
-        <v>33.95</v>
+        <v>34.23</v>
       </c>
       <c r="C318" s="2" t="n">
-        <v>10107</v>
+        <v>13364</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>785056</v>
+        <v>939655</v>
       </c>
     </row>
     <row r="319">
@@ -5875,13 +5881,13 @@
         <v>321</v>
       </c>
       <c r="B319" s="2" t="n">
-        <v>33.33</v>
+        <v>34.14</v>
       </c>
       <c r="C319" s="2" t="n">
-        <v>881</v>
+        <v>12432</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>850000</v>
+        <v>672043</v>
       </c>
     </row>
     <row r="320">
@@ -5889,13 +5895,13 @@
         <v>322</v>
       </c>
       <c r="B320" s="2" t="n">
-        <v>33.18</v>
+        <v>33.95</v>
       </c>
       <c r="C320" s="2" t="n">
-        <v>9269</v>
+        <v>10107</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>875000</v>
+        <v>785056</v>
       </c>
     </row>
     <row r="321">
@@ -5903,13 +5909,13 @@
         <v>323</v>
       </c>
       <c r="B321" s="2" t="n">
-        <v>33.02</v>
+        <v>33.33</v>
       </c>
       <c r="C321" s="2" t="n">
-        <v>1335</v>
+        <v>881</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>845239.5</v>
+        <v>850000</v>
       </c>
     </row>
     <row r="322">
@@ -5917,13 +5923,13 @@
         <v>324</v>
       </c>
       <c r="B322" s="2" t="n">
-        <v>32.48</v>
+        <v>33.18</v>
       </c>
       <c r="C322" s="2" t="n">
-        <v>4885</v>
+        <v>9269</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>757377</v>
+        <v>875000</v>
       </c>
     </row>
     <row r="323">
@@ -5931,13 +5937,13 @@
         <v>325</v>
       </c>
       <c r="B323" s="2" t="n">
-        <v>31.31</v>
+        <v>33.02</v>
       </c>
       <c r="C323" s="2" t="n">
-        <v>7096</v>
+        <v>1335</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>981497</v>
+        <v>845239.5</v>
       </c>
     </row>
     <row r="324">
@@ -5945,13 +5951,13 @@
         <v>326</v>
       </c>
       <c r="B324" s="2" t="n">
-        <v>31.28</v>
+        <v>32.48</v>
       </c>
       <c r="C324" s="2" t="n">
-        <v>9129</v>
+        <v>4885</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>575000</v>
+        <v>757377</v>
       </c>
     </row>
     <row r="325">
@@ -5959,13 +5965,13 @@
         <v>327</v>
       </c>
       <c r="B325" s="2" t="n">
-        <v>31.28</v>
+        <v>31.31</v>
       </c>
       <c r="C325" s="2" t="n">
-        <v>32260</v>
+        <v>7096</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>912500</v>
+        <v>981497</v>
       </c>
     </row>
     <row r="326">
@@ -5973,13 +5979,13 @@
         <v>328</v>
       </c>
       <c r="B326" s="2" t="n">
-        <v>30.37</v>
+        <v>31.28</v>
       </c>
       <c r="C326" s="2" t="n">
-        <v>19193</v>
+        <v>9129</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>974600</v>
+        <v>575000</v>
       </c>
     </row>
     <row r="327">
@@ -5987,13 +5993,13 @@
         <v>329</v>
       </c>
       <c r="B327" s="2" t="n">
-        <v>29.01</v>
+        <v>31.28</v>
       </c>
       <c r="C327" s="2" t="n">
-        <v>7980</v>
+        <v>32260</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>686827</v>
+        <v>912500</v>
       </c>
     </row>
     <row r="328">
@@ -6001,17 +6007,45 @@
         <v>330</v>
       </c>
       <c r="B328" s="2" t="n">
+        <v>30.37</v>
+      </c>
+      <c r="C328" s="2" t="n">
+        <v>19193</v>
+      </c>
+      <c r="D328" s="2" t="n">
+        <v>974600</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B329" s="2" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="C329" s="2" t="n">
+        <v>7980</v>
+      </c>
+      <c r="D329" s="2" t="n">
+        <v>686827</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B330" s="2" t="n">
         <v>26.46</v>
       </c>
-      <c r="C328" s="2" t="n">
+      <c r="C330" s="2" t="n">
         <v>9476</v>
       </c>
-      <c r="D328" s="2" t="n">
+      <c r="D330" s="2" t="n">
         <v>655613</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D328"/>
+  <autoFilter ref="A1:D330"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -6028,7 +6062,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -6036,50 +6070,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
